--- a/output/pdf_financials_xlsx/SYG.xlsx
+++ b/output/pdf_financials_xlsx/SYG.xlsx
@@ -6264,25 +6264,25 @@
         <v>0.37444</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.301</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.328</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.2962</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.2962</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.2962</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.277</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.277</v>
       </c>
       <c r="L92" s="3" t="n">
         <v>0</v>
@@ -12810,7 +12810,11 @@
           <t>Reserves (Note 12)</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -13604,7 +13608,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -14106,7 +14114,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -14830,7 +14842,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
@@ -16006,7 +16022,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SYG.xlsx
+++ b/output/pdf_financials_xlsx/SYG.xlsx
@@ -1101,7 +1101,7 @@
         <v>0</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.0006489999999999999</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>0</v>
@@ -2102,7 +2102,7 @@
         <v>-0.111025</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.06911100000000001</v>
+        <v>0.068462</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>0.06911100000000001</v>
@@ -2224,7 +2224,7 @@
         <v>-0.111025</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.06911100000000001</v>
+        <v>0.068462</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>0.06911100000000001</v>
@@ -2507,58 +2507,58 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.219869</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.179001</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.00291</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.036696</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.007382</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.001084</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.000123</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>7.3e-05</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.005033</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.003112</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.001352</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.00061</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.000301</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.020106</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.012066</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.001237</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>1.71245</v>
       </c>
     </row>
     <row r="35">
@@ -2629,58 +2629,58 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.219869</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.179001</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.00291</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.036696</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.007382</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.001084</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.000123</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>7.3e-05</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.005033</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.003112</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.001352</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.00061</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.000301</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.020106</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.012066</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.001237</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>1.71245</v>
       </c>
     </row>
     <row r="37">
@@ -3364,55 +3364,55 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.19058</v>
+        <v>0.011579</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.028282</v>
+        <v>0.025372</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.07890900000000001</v>
+        <v>0.042213</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.01905</v>
+        <v>0.011668</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.031117</v>
+        <v>0.030033</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.011005</v>
+        <v>0.010882</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.004989</v>
+        <v>0.004916</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.006807</v>
+        <v>0.001774</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.003112</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.001352</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.00061</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.014301</v>
+        <v>0.014</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.111329</v>
+        <v>0.091223</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.12866</v>
+        <v>0.116594</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.039446</v>
+        <v>0.028446</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.007986999999999999</v>
+        <v>0.00675</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>1.723734</v>
+        <v>0.011284</v>
       </c>
     </row>
     <row r="49">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -16992,7 +16992,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E77" s="5" t="n">
@@ -34884,7 +34884,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -36582,7 +36582,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">

--- a/output/pdf_financials_xlsx/SYG.xlsx
+++ b/output/pdf_financials_xlsx/SYG.xlsx
@@ -776,13 +776,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.025743</v>
+        <v>0.030547</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.017003</v>
+        <v>0.017253</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.02308</v>
+        <v>0.025005</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0.013353</v>
@@ -959,13 +959,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.025743</v>
+        <v>0.030547</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.017003</v>
+        <v>0.017253</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.02308</v>
+        <v>0.025005</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>0.013353</v>
@@ -1022,7 +1022,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.025743</v>
+        <v>-0.030547</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>-0.031593</v>
@@ -1379,13 +1379,13 @@
         <v>-0</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.002934</v>
+        <v>-0.002934</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.018316</v>
+        <v>-0.018316</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.015</v>
+        <v>-0.015</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>-0</v>
@@ -4639,49 +4639,49 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.11482</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.18078</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.08207200000000001</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.08543199999999999</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.08457199999999999</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.08457199999999999</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.122072</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.028572</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.036572</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.0301</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.029666</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.038763</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.06876</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>0.06833500000000001</v>
       </c>
       <c r="S67" s="3" t="n">
-        <v>0</v>
+        <v>0.070602</v>
       </c>
     </row>
     <row r="68">
@@ -7428,7 +7428,7 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.048207</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
@@ -8911,7 +8911,7 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.048207</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
@@ -19592,7 +19592,11 @@
           <t>Units issued by private placement</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
@@ -25288,7 +25292,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
           <t>-</t>
@@ -28580,7 +28588,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E188" s="5" t="n">
         <v>-0.002141</v>
       </c>
@@ -30174,7 +30186,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E203" s="5" t="n">
         <v>-0.048207</v>
       </c>
@@ -40262,7 +40278,11 @@
           <t>Office expense</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr"/>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E299" t="inlineStr">
         <is>
           <t>-</t>
@@ -42458,7 +42478,11 @@
           <t>Deferred Income Tax Recovery</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr"/>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E320" t="inlineStr">
         <is>
           <t>-</t>
